--- a/Results/Summary.xlsx
+++ b/Results/Summary.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shaun Tonstad\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Source\unity-birp-vs-urp-performance\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B7E56B7-B22D-4FA2-A3C0-CEDA394244EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D39E519E-2771-4D13-BEBF-5292969A820B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="51420" windowHeight="21100" xr2:uid="{063CB107-2C1C-4A1E-A4C3-45183028293E}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="21">
   <si>
     <t>GTX 1650</t>
   </si>
@@ -178,11 +178,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -8251,15 +8250,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>425450</xdr:colOff>
+      <xdr:colOff>213360</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:rowOff>22860</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>450850</xdr:colOff>
+      <xdr:colOff>236220</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:rowOff>7620</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -8286,16 +8285,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>31750</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>596900</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>146050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>31</xdr:col>
-      <xdr:colOff>336550</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>177800</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -8323,15 +8322,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>15240</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>209550</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -8359,15 +8358,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>438150</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>88900</xdr:rowOff>
+      <xdr:colOff>213360</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>15240</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>463550</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>69850</xdr:rowOff>
+      <xdr:colOff>236220</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>175260</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -8394,16 +8393,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>50800</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>203200</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>31</xdr:col>
-      <xdr:colOff>355600</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -8430,16 +8429,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>133350</xdr:colOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>25400</xdr:rowOff>
+      <xdr:rowOff>16510</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>438150</xdr:colOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>6350</xdr:rowOff>
+      <xdr:rowOff>2540</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -8466,16 +8465,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>158750</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>107950</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>259080</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>22860</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>463550</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>88900</xdr:rowOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>563880</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>8890</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -8502,16 +8501,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>6350</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>73025</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>603250</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>79375</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>196850</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>53975</xdr:rowOff>
+      <xdr:colOff>184150</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>60325</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -8866,55 +8865,57 @@
   </cols>
   <sheetData>
     <row r="2" spans="3:24" x14ac:dyDescent="0.35">
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="I2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="L2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="M2" s="5" t="s">
+      <c r="M2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="5" t="s">
+      <c r="N2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="O2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="P2" s="5" t="s">
+      <c r="P2" s="4" t="s">
         <v>3</v>
       </c>
       <c r="Q2" s="1"/>
-      <c r="R2" s="5" t="s">
+      <c r="R2" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="S2" s="6"/>
-      <c r="T2" s="6"/>
-      <c r="U2" s="5" t="s">
+      <c r="S2" s="5"/>
+      <c r="T2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="U2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="W2" s="5" t="s">
+      <c r="W2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="X2" s="5" t="s">
+      <c r="X2" s="4" t="s">
         <v>20</v>
       </c>
     </row>
@@ -8940,8 +8941,8 @@
       <c r="I3" s="2">
         <v>114</v>
       </c>
-      <c r="L3" s="3" t="str">
-        <f>_xlfn.TEXTJOIN(" ", FALSE, C3:E3)</f>
+      <c r="L3" s="2" t="str">
+        <f t="shared" ref="L3:L10" si="0">_xlfn.TEXTJOIN(" ", FALSE, C3:E3)</f>
         <v>GTX 1650 DX11 BIRP</v>
       </c>
       <c r="M3" s="2">
@@ -8999,23 +9000,23 @@
         <v>103.5</v>
       </c>
       <c r="L4" s="2" t="str">
-        <f>_xlfn.TEXTJOIN(" ", FALSE, C4:E4)</f>
+        <f t="shared" si="0"/>
         <v>GTX 1650 DX12 BIRP</v>
       </c>
       <c r="M4" s="2">
-        <f t="shared" ref="M4:M10" si="0">F4</f>
+        <f t="shared" ref="M4:M10" si="1">F4</f>
         <v>9.65</v>
       </c>
       <c r="N4" s="2">
-        <f t="shared" ref="N4:N10" si="1">G4</f>
+        <f t="shared" ref="N4:N10" si="2">G4</f>
         <v>6.65</v>
       </c>
       <c r="O4" s="2">
-        <f t="shared" ref="O4:O10" si="2">H4</f>
+        <f t="shared" ref="O4:O10" si="3">H4</f>
         <v>9.66</v>
       </c>
       <c r="P4" s="2">
-        <f t="shared" ref="P4:P10" si="3">I4</f>
+        <f t="shared" ref="P4:P10" si="4">I4</f>
         <v>103.5</v>
       </c>
       <c r="R4" s="2" t="s">
@@ -9026,7 +9027,7 @@
         <f>H6</f>
         <v>11.98</v>
       </c>
-      <c r="U4" s="4">
+      <c r="U4" s="3">
         <f>(T4-T3)/T3</f>
         <v>0.36602052451539352</v>
       </c>
@@ -9060,23 +9061,23 @@
         <v>105.3</v>
       </c>
       <c r="L5" s="2" t="str">
-        <f>_xlfn.TEXTJOIN(" ", FALSE, C5:E5)</f>
+        <f t="shared" si="0"/>
         <v>GTX 1650 DX11 URP</v>
       </c>
       <c r="M5" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>9.42</v>
       </c>
       <c r="N5" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>5.13</v>
       </c>
       <c r="O5" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>9.5</v>
       </c>
       <c r="P5" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>105.3</v>
       </c>
       <c r="R5" s="2" t="s">
@@ -9112,23 +9113,23 @@
         <v>83.5</v>
       </c>
       <c r="L6" s="2" t="str">
-        <f>_xlfn.TEXTJOIN(" ", FALSE, C6:E6)</f>
+        <f t="shared" si="0"/>
         <v>GTX 1650 DX12 URP</v>
       </c>
       <c r="M6" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>11.95</v>
       </c>
       <c r="N6" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>5.66</v>
       </c>
       <c r="O6" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>11.98</v>
       </c>
       <c r="P6" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>83.5</v>
       </c>
       <c r="R6" s="2" t="s">
@@ -9139,7 +9140,7 @@
         <f>H10</f>
         <v>1.64</v>
       </c>
-      <c r="U6" s="4">
+      <c r="U6" s="3">
         <f>(T6-T5)/T5</f>
         <v>1.0759493670886073</v>
       </c>
@@ -9167,23 +9168,23 @@
         <v>1268.9000000000001</v>
       </c>
       <c r="L7" s="2" t="str">
-        <f>_xlfn.TEXTJOIN(" ", FALSE, C7:E7)</f>
+        <f t="shared" si="0"/>
         <v>RTX 4090 DX11 BIRP</v>
       </c>
       <c r="M7" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.78</v>
       </c>
       <c r="N7" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.76</v>
       </c>
       <c r="O7" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0.79</v>
       </c>
       <c r="P7" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1268.9000000000001</v>
       </c>
     </row>
@@ -9210,23 +9211,23 @@
         <v>863</v>
       </c>
       <c r="L8" s="2" t="str">
-        <f>_xlfn.TEXTJOIN(" ", FALSE, C8:E8)</f>
+        <f t="shared" si="0"/>
         <v>RTX 4090 DX12 BIRP</v>
       </c>
       <c r="M8" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.1599999999999999</v>
       </c>
       <c r="N8" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.94</v>
       </c>
       <c r="O8" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.1599999999999999</v>
       </c>
       <c r="P8" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>863</v>
       </c>
     </row>
@@ -9253,23 +9254,23 @@
         <v>864.2</v>
       </c>
       <c r="L9" s="2" t="str">
-        <f>_xlfn.TEXTJOIN(" ", FALSE, C9:E9)</f>
+        <f t="shared" si="0"/>
         <v>RTX 4090 DX11 URP</v>
       </c>
       <c r="M9" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.1200000000000001</v>
       </c>
       <c r="N9" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.77</v>
       </c>
       <c r="O9" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.1599999999999999</v>
       </c>
       <c r="P9" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>864.2</v>
       </c>
     </row>
@@ -9296,23 +9297,23 @@
         <v>610.4</v>
       </c>
       <c r="L10" s="2" t="str">
-        <f>_xlfn.TEXTJOIN(" ", FALSE, C10:E10)</f>
+        <f t="shared" si="0"/>
         <v>RTX 4090 DX12  URP</v>
       </c>
       <c r="M10" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.61</v>
       </c>
       <c r="N10" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.83</v>
       </c>
       <c r="O10" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.64</v>
       </c>
       <c r="P10" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>610.4</v>
       </c>
     </row>

--- a/Results/Summary.xlsx
+++ b/Results/Summary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Source\unity-birp-vs-urp-performance\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D39E519E-2771-4D13-BEBF-5292969A820B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12336A37-C177-47B0-A778-6CED643F60F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="51420" windowHeight="21100" xr2:uid="{063CB107-2C1C-4A1E-A4C3-45183028293E}"/>
+    <workbookView xWindow="24910" yWindow="0" windowWidth="25780" windowHeight="20970" xr2:uid="{063CB107-2C1C-4A1E-A4C3-45183028293E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="20">
   <si>
     <t>GTX 1650</t>
   </si>
@@ -60,9 +60,6 @@
   </si>
   <si>
     <t>RTX 4090</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> URP</t>
   </si>
   <si>
     <t>Frame</t>
@@ -317,6 +314,44 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000002-4C57-4F42-9222-F063B02C7613}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000002-3F41-4E91-9E7D-15E090A83700}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
                 <a:schemeClr val="accent2"/>
               </a:solidFill>
               <a:ln>
@@ -326,7 +361,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000002-4C57-4F42-9222-F063B02C7613}"/>
+                <c16:uniqueId val="{00000003-3F41-4E91-9E7D-15E090A83700}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -363,10 +398,10 @@
                   <c:v>9.65</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>9.42</c:v>
+                  <c:v>8.41</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>11.95</c:v>
+                  <c:v>11.43</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -715,10 +750,10 @@
                   <c:v>6.65</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5.13</c:v>
+                  <c:v>4.42</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5.66</c:v>
+                  <c:v>5.0999999999999996</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1020,6 +1055,25 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-AB4D-44D7-B016-AC3468EBAAD8}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
                 <a:schemeClr val="accent2"/>
               </a:solidFill>
               <a:ln>
@@ -1029,7 +1083,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-AB4D-44D7-B016-AC3468EBAAD8}"/>
+                <c16:uniqueId val="{00000002-126C-4138-BE77-E07B0BEA9419}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1066,10 +1120,10 @@
                   <c:v>103.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>105.3</c:v>
+                  <c:v>117.2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>83.5</c:v>
+                  <c:v>82.4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1389,7 +1443,7 @@
                   <c:v>RTX 4090 DX11 URP</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>RTX 4090 DX12  URP</c:v>
+                  <c:v>RTX 4090 DX12 URP</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1407,10 +1461,10 @@
                   <c:v>1.1599999999999999</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.1200000000000001</c:v>
+                  <c:v>0.92</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.61</c:v>
+                  <c:v>1.36</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1702,6 +1756,25 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-608E-4F9B-A5AD-B7018EE3A269}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
                 <a:schemeClr val="accent2"/>
               </a:solidFill>
               <a:ln>
@@ -1711,7 +1784,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-608E-4F9B-A5AD-B7018EE3A269}"/>
+                <c16:uniqueId val="{00000002-B20F-4335-A212-E31D73E00D61}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1730,7 +1803,7 @@
                   <c:v>RTX 4090 DX11 URP</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>RTX 4090 DX12  URP</c:v>
+                  <c:v>RTX 4090 DX12 URP</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1748,10 +1821,10 @@
                   <c:v>0.94</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.77</c:v>
+                  <c:v>0.64</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.83</c:v>
+                  <c:v>0.74</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2071,7 +2144,7 @@
                   <c:v>RTX 4090 DX11 URP</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>RTX 4090 DX12  URP</c:v>
+                  <c:v>RTX 4090 DX12 URP</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2089,10 +2162,10 @@
                   <c:v>863</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>864.2</c:v>
+                  <c:v>1028.7</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>610.4</c:v>
+                  <c:v>723.1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2405,6 +2478,25 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-46AB-46A9-B22D-022A5ACFB0FC}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
                 <a:schemeClr val="accent2"/>
               </a:solidFill>
               <a:ln>
@@ -2414,7 +2506,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-46AB-46A9-B22D-022A5ACFB0FC}"/>
+                <c16:uniqueId val="{00000002-40E6-4F11-AA65-8C21F84074FC}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -2451,10 +2543,10 @@
                   <c:v>9.66</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>9.5</c:v>
+                  <c:v>8.5299999999999994</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>11.98</c:v>
+                  <c:v>12.14</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2783,7 +2875,7 @@
                   <c:v>RTX 4090 DX11 URP</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>RTX 4090 DX12  URP</c:v>
+                  <c:v>RTX 4090 DX12 URP</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2801,10 +2893,10 @@
                   <c:v>1.1599999999999999</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.1599999999999999</c:v>
+                  <c:v>0.97</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.64</c:v>
+                  <c:v>1.38</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8875,48 +8967,48 @@
         <v>4</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>1</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I2" s="4" t="s">
         <v>3</v>
       </c>
       <c r="L2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="M2" s="4" t="s">
         <v>10</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>11</v>
       </c>
       <c r="N2" s="4" t="s">
         <v>1</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P2" s="4" t="s">
         <v>3</v>
       </c>
       <c r="Q2" s="1"/>
       <c r="R2" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="S2" s="5"/>
       <c r="T2" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U2" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="W2" s="4" t="s">
         <v>4</v>
       </c>
       <c r="X2" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="3:24" x14ac:dyDescent="0.35">
@@ -8924,7 +9016,7 @@
         <v>0</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>5</v>
@@ -8962,7 +9054,7 @@
         <v>114</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="S3" s="2"/>
       <c r="T3" s="2">
@@ -8982,7 +9074,7 @@
         <v>0</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>5</v>
@@ -9020,16 +9112,16 @@
         <v>103.5</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="S4" s="2"/>
       <c r="T4" s="2">
         <f>H6</f>
-        <v>11.98</v>
+        <v>12.14</v>
       </c>
       <c r="U4" s="3">
         <f>(T4-T3)/T3</f>
-        <v>0.36602052451539352</v>
+        <v>0.38426453819840378</v>
       </c>
       <c r="W4" s="2" t="s">
         <v>6</v>
@@ -9043,22 +9135,22 @@
         <v>0</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F5" s="2">
-        <v>9.42</v>
+        <v>8.41</v>
       </c>
       <c r="G5" s="2">
-        <v>5.13</v>
+        <v>4.42</v>
       </c>
       <c r="H5" s="2">
-        <v>9.5</v>
+        <v>8.5299999999999994</v>
       </c>
       <c r="I5" s="2">
-        <v>105.3</v>
+        <v>117.2</v>
       </c>
       <c r="L5" s="2" t="str">
         <f t="shared" si="0"/>
@@ -9066,22 +9158,22 @@
       </c>
       <c r="M5" s="2">
         <f t="shared" si="1"/>
-        <v>9.42</v>
+        <v>8.41</v>
       </c>
       <c r="N5" s="2">
         <f t="shared" si="2"/>
-        <v>5.13</v>
+        <v>4.42</v>
       </c>
       <c r="O5" s="2">
         <f t="shared" si="3"/>
-        <v>9.5</v>
+        <v>8.5299999999999994</v>
       </c>
       <c r="P5" s="2">
         <f t="shared" si="4"/>
-        <v>105.3</v>
+        <v>117.2</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="S5" s="2"/>
       <c r="T5" s="2">
@@ -9095,22 +9187,22 @@
         <v>0</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F6" s="2">
-        <v>11.95</v>
+        <v>11.43</v>
       </c>
       <c r="G6" s="2">
-        <v>5.66</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="H6" s="2">
-        <v>11.98</v>
+        <v>12.14</v>
       </c>
       <c r="I6" s="2">
-        <v>83.5</v>
+        <v>82.4</v>
       </c>
       <c r="L6" s="2" t="str">
         <f t="shared" si="0"/>
@@ -9118,31 +9210,31 @@
       </c>
       <c r="M6" s="2">
         <f t="shared" si="1"/>
-        <v>11.95</v>
+        <v>11.43</v>
       </c>
       <c r="N6" s="2">
         <f t="shared" si="2"/>
-        <v>5.66</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="O6" s="2">
         <f t="shared" si="3"/>
-        <v>11.98</v>
+        <v>12.14</v>
       </c>
       <c r="P6" s="2">
         <f t="shared" si="4"/>
-        <v>83.5</v>
+        <v>82.4</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="S6" s="2"/>
       <c r="T6" s="2">
         <f>H10</f>
-        <v>1.64</v>
+        <v>1.38</v>
       </c>
       <c r="U6" s="3">
         <f>(T6-T5)/T5</f>
-        <v>1.0759493670886073</v>
+        <v>0.74683544303797444</v>
       </c>
     </row>
     <row r="7" spans="3:24" x14ac:dyDescent="0.35">
@@ -9150,7 +9242,7 @@
         <v>7</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>5</v>
@@ -9193,7 +9285,7 @@
         <v>7</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>5</v>
@@ -9236,22 +9328,22 @@
         <v>7</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F9" s="2">
-        <v>1.1200000000000001</v>
+        <v>0.92</v>
       </c>
       <c r="G9" s="2">
-        <v>0.77</v>
+        <v>0.64</v>
       </c>
       <c r="H9" s="2">
-        <v>1.1599999999999999</v>
+        <v>0.97</v>
       </c>
       <c r="I9" s="2">
-        <v>864.2</v>
+        <v>1028.7</v>
       </c>
       <c r="L9" s="2" t="str">
         <f t="shared" si="0"/>
@@ -9259,19 +9351,19 @@
       </c>
       <c r="M9" s="2">
         <f t="shared" si="1"/>
-        <v>1.1200000000000001</v>
+        <v>0.92</v>
       </c>
       <c r="N9" s="2">
         <f t="shared" si="2"/>
-        <v>0.77</v>
+        <v>0.64</v>
       </c>
       <c r="O9" s="2">
         <f t="shared" si="3"/>
-        <v>1.1599999999999999</v>
+        <v>0.97</v>
       </c>
       <c r="P9" s="2">
         <f t="shared" si="4"/>
-        <v>864.2</v>
+        <v>1028.7</v>
       </c>
     </row>
     <row r="10" spans="3:24" x14ac:dyDescent="0.35">
@@ -9279,42 +9371,42 @@
         <v>7</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F10" s="2">
-        <v>1.61</v>
+        <v>1.36</v>
       </c>
       <c r="G10" s="2">
-        <v>0.83</v>
+        <v>0.74</v>
       </c>
       <c r="H10" s="2">
-        <v>1.64</v>
+        <v>1.38</v>
       </c>
       <c r="I10" s="2">
-        <v>610.4</v>
+        <v>723.1</v>
       </c>
       <c r="L10" s="2" t="str">
         <f t="shared" si="0"/>
-        <v>RTX 4090 DX12  URP</v>
+        <v>RTX 4090 DX12 URP</v>
       </c>
       <c r="M10" s="2">
         <f t="shared" si="1"/>
-        <v>1.61</v>
+        <v>1.36</v>
       </c>
       <c r="N10" s="2">
         <f t="shared" si="2"/>
-        <v>0.83</v>
+        <v>0.74</v>
       </c>
       <c r="O10" s="2">
         <f t="shared" si="3"/>
-        <v>1.64</v>
+        <v>1.38</v>
       </c>
       <c r="P10" s="2">
         <f t="shared" si="4"/>
-        <v>610.4</v>
+        <v>723.1</v>
       </c>
     </row>
   </sheetData>
